--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swati Spentose Private Limited, Unit-Ii.</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dutasterida</t>
+          <t>cloridrato de sertralina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351312251202380</t>
+          <t>25351114179202246</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,385 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>propionato de fluticasona</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25351088020202421</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>levetiracetam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25351078614202423</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>vismodegibe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25351045971202677</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shilpa Pharma Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mesilato de lenvatinibe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25351017275202590</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cloridrato de atomoxetina</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25351114320202553</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Asolution Pharmaceuticals Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sugamadex sódico</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25351793830202150</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Harman Finochem Limited</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hemitartarato de norepinefrina monoidratada</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25351358693202453</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Synthon Bv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lenalidomida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25351807850202387</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lacosamida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25351226464202551</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wanbury Limited</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cloridrato de metformina</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25351454913202479</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Honour Lab Limited</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>empagliflozina</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>25351427875202481</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hetero Drugs Limited</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mirtazapina</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25351268546202310</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dapagliflozina propanodiol monoidratado</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25351355090202408</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Xellia Pharmaceuticals Aps</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>anfotericina b</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25351860617202322</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Bec Chemicals Private Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cloridrato de sertralina</t>
+          <t>cetoprofeno</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351114179202246</t>
+          <t>25351184842202351</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,385 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>propionato de fluticasona</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>25351088020202421</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>levetiracetam</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25351078614202423</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>vismodegibe</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25351045971202677</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Shilpa Pharma Lifesciences Limited</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mesilato de lenvatinibe</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25351017275202590</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hetero Labs Limited</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>cloridrato de atomoxetina</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>25351114320202553</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Asolution Pharmaceuticals Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sugamadex sódico</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>25351793830202150</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Harman Finochem Limited</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>hemitartarato de norepinefrina monoidratada</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>25351358693202453</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Synthon Bv</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lenalidomida</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>25351807850202387</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>lacosamida</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>25351226464202551</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Wanbury Limited</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cloridrato de metformina</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>25351454913202479</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Honour Lab Limited</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>empagliflozina</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>25351427875202481</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Hetero Drugs Limited</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>mirtazapina</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>25351268546202310</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>dapagliflozina propanodiol monoidratado</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>25351355090202408</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Xellia Pharmaceuticals Aps</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>anfotericina b</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>25351860617202322</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bec Chemicals Private Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cetoprofeno</t>
+          <t>dasatinibe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351184842202351</t>
+          <t>25351301199202336</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,601 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Divi'S Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gabapentina</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25351881372202377</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>anastrozol</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25351780323202318</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>valsartana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25351568503202242</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shakti Lifescience Private Limited</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>valerato de estradiol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25351401058202401</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alembic Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bromidrato de vortioxetina</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25351504054202395</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Emcure Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cloridrato de dexmedetomidina</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25351200072202309</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cipla Limited</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>exemestano</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25351112796202398</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Targo Comércio Internacional Limitada</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cloridrato de cefepima</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25351418624202325</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bdr Lifesciences Private Limited</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lenalidomida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25351368762202437</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pitavastatina cálcica pentaidratada</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25351364931202389</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Honour Lab Limited</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>citrato de tofacitinibe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>25351004248202638</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Angelini Pharma S.P.A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cloridrato de trazodona</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25351645542202271</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Msn Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cloridrato de pioglitazona</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25351352149202317</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lenalidomida</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25351259463202411</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Laurus Labs Limited</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lenalidomida</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25351964289202413</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>desloratadina</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>25351423976202301</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Angelini Pharma S.P.A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cloridrato de trazodona</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25351415967202419</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cadila Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>loratadina</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25351302160202255</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Zhejiang Tianyu Pharmaceutical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>losartana potássica</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>25351150973202415</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Keshava Organics Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>maleato de clorfeniramina</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25351150943202328</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>letrozol</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25351220214202265</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Msn Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cloridrato de atomoxetina</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25351138602202546</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Teva Farmacêutica Ltda.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dasatinibe</t>
+          <t>cloridrato de daunorrubicina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351301199202336</t>
+          <t>25351415971202487</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,24 +466,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Divi'S Laboratories Limited</t>
+          <t>Micro Labs Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gabapentina</t>
+          <t>tartarato de brimonidina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25351881372202377</t>
+          <t>25351584936202326</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,24 +493,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Hikal Limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>anastrozol</t>
+          <t>pregabalina</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25351780323202318</t>
+          <t>25351169043202192</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,24 +520,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
+          <t>Msn Pharmachem Private Limited</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>valsartana</t>
+          <t>cloridrato de moxifloxacino</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25351568503202242</t>
+          <t>25351941006202465</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,24 +547,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shakti Lifescience Private Limited</t>
+          <t>Fersinsa Gb S.A. De C.V.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>valerato de estradiol</t>
+          <t>amoxicilina tri-hidratada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25351401058202401</t>
+          <t>25351400200202312</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Vasudha Pharma Chem Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bromidrato de vortioxetina</t>
+          <t>loratadina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25351504054202395</t>
+          <t>25351233832202275</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cloridrato de dexmedetomidina</t>
+          <t>bissulfato de clopidogrel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25351200072202309</t>
+          <t>25351135853202498</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Chifeng Arker Pharmaceutical Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exemestano</t>
+          <t>cloridrato de pseudoefedrina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25351112796202398</t>
+          <t>25351533438202315</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Targo Comércio Internacional Limitada</t>
+          <t>Laurus Labs Limited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cloridrato de cefepima</t>
+          <t>enzalutamida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25351418624202325</t>
+          <t>25351001382202415</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,385 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Bdr Lifesciences Private Limited</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>lenalidomida</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>25351368762202437</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma Sciences Limited</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>pitavastatina cálcica pentaidratada</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>25351364931202389</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Honour Lab Limited</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>citrato de tofacitinibe</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>25351004248202638</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Angelini Pharma S.P.A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>cloridrato de trazodona</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>25351645542202271</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Msn Organics Private Limited</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>cloridrato de pioglitazona</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>25351352149202317</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Hetero Labs Limited</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>lenalidomida</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>25351259463202411</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Laurus Labs Limited</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>lenalidomida</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>25351964289202413</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Zydus Lifesciences Limited</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>desloratadina</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>25351423976202301</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Angelini Pharma S.P.A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>cloridrato de trazodona</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>25351415967202419</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Cadila Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>loratadina</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>25351302160202255</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Zhejiang Tianyu Pharmaceutical Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>losartana potássica</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>25351150973202415</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Keshava Organics Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>maleato de clorfeniramina</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>25351150943202328</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Hetero Labs Limited</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>letrozol</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>25351220214202265</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Msn Organics Private Limited</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>cloridrato de atomoxetina</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>25351138602202546</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Teva Farmacêutica Ltda.</t>
+          <t>Harman Finochem Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cloridrato de daunorrubicina</t>
+          <t>hemifumarato de bisoprolol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351415971202487</t>
+          <t>25351370849202474</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,24 +466,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Micro Labs Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tartarato de brimonidina</t>
+          <t>cloridrato de duloxetina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25351584936202326</t>
+          <t>25351325434202365</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,24 +493,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>Chr. Olesen Synthesis A/S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pregabalina</t>
+          <t>dimesilato de lisdexanfetamina</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25351169043202192</t>
+          <t>25351423008202477</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,24 +520,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Msn Pharmachem Private Limited</t>
+          <t>Kolon Life Science, Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cloridrato de moxifloxacino</t>
+          <t>pitavastatina cálcica pentaidratada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25351941006202465</t>
+          <t>25351265518202332</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,142 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fersinsa Gb S.A. De C.V.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>amoxicilina tri-hidratada</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25351400200202312</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Vasudha Pharma Chem Limited</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>loratadina</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>25351233832202275</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>bissulfato de clopidogrel</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>25351135853202498</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chifeng Arker Pharmaceutical Technology Co.,Ltd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>cloridrato de pseudoefedrina</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>25351533438202315</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Laurus Labs Limited</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>enzalutamida</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>25351001382202415</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Harman Finochem Limited</t>
+          <t>Euroapi Germany Gmbh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hemifumarato de bisoprolol</t>
+          <t>dipirona monoidratada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351370849202474</t>
+          <t>25351230892202317</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,87 +465,6 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Alembic Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>cloridrato de duloxetina</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>25351325434202365</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chr. Olesen Synthesis A/S</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>dimesilato de lisdexanfetamina</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25351423008202477</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kolon Life Science, Inc.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pitavastatina cálcica pentaidratada</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25351265518202332</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Euroapi Germany Gmbh</t>
+          <t>Msn Life Sciences Private Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dipirona monoidratada</t>
+          <t>esomeprazol sódico</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351230892202317</t>
+          <t>25351364636202411</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,277 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Harman Finochem Limited</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cloridrato de metilfenidato</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25351231414202596</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alivus Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>desloratadina</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25351849706202318</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Produtos Farmacêuticos Ltda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>olanzapina</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25351032619202591</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chromo Laboratories India Private Limited</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>voriconazol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25351102482202387</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jiangsu Hengrui Pharmaceuticals Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>acetato de caspofungina</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25351584854202381</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cloridrato de nilotinibe monoidratado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25351529258202339</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Msn Life Sciences Private Limited</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>semaglutida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25351451318202481</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hetero Drugs Limited</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>besilato de anlodipino</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25351359224202371</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bosutinibe di-hidratado</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25351146014202586</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ticagrelor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25351060071202498</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shanghai Pharma Group Changzhou Kony Pharmaceutical Co., Ltd.</t>
+          <t>Bridgebio Pharma, Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cloridrato de valganciclovir</t>
+          <t>cloridrato de acoramidis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351830462202308</t>
+          <t>25351209898202414</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,142 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ajinomoto Co., Inc.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>levodopa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>25351227633202490</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Globe Quimica Ltda.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>cloridrato de midazolam</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25351079731202595</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Harman Finochem Limited</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sacubitril valsartana sódica hidratada</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25351934362202422</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alembic Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sacubitril valsartana sódica hidratada</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25351444971202494</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jiangxi Synergy Pharmaceutical Co., Ltd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>empagliflozina</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>25351158698202569</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
+          <t>09/12/2025</t>
         </is>
       </c>
     </row>
